--- a/output_3a.xlsx
+++ b/output_3a.xlsx
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>369352.8</v>
+        <v>369326.8</v>
       </c>
     </row>
     <row r="4">
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>133.33</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5">
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6272</v>
+        <v>6312</v>
       </c>
     </row>
     <row r="6">
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>521258.13</v>
+        <v>521270.8</v>
       </c>
     </row>
   </sheetData>
@@ -547,10 +547,10 @@
         <v>32500</v>
       </c>
       <c r="D2" t="n">
-        <v>42276</v>
+        <v>42282</v>
       </c>
       <c r="E2" t="n">
-        <v>74776</v>
+        <v>74782</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
@@ -673,10 +673,10 @@
         <v>27000</v>
       </c>
       <c r="D8" t="n">
-        <v>148418</v>
+        <v>148386</v>
       </c>
       <c r="E8" t="n">
-        <v>175418</v>
+        <v>175386</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
@@ -694,16 +694,16 @@
         <v>145500</v>
       </c>
       <c r="D9" t="n">
-        <v>369352.8</v>
+        <v>369326.8</v>
       </c>
       <c r="E9" t="n">
-        <v>514852.8</v>
+        <v>514826.8</v>
       </c>
       <c r="F9" t="n">
-        <v>133.33</v>
+        <v>132</v>
       </c>
       <c r="G9" t="n">
-        <v>6272</v>
+        <v>6312</v>
       </c>
     </row>
   </sheetData>
@@ -757,19 +757,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="3">
@@ -777,19 +777,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="4">
@@ -797,19 +797,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="5">
@@ -817,19 +817,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="6">
@@ -837,19 +837,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="7">
@@ -857,19 +857,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="8">
@@ -877,19 +877,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="9">
@@ -900,16 +900,16 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="10">
@@ -917,19 +917,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="11">
@@ -937,19 +937,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="12">
@@ -957,19 +957,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="13">
@@ -977,19 +977,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -997,19 +997,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="15">
@@ -1020,16 +1020,16 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="16">
@@ -1037,19 +1037,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>33.3</v>
+        <v>33</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E16" t="n">
-        <v>66.67</v>
+        <v>66</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="17">
@@ -1057,19 +1057,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -1077,19 +1077,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -1097,19 +1097,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C19" t="n">
-        <v>856</v>
+        <v>875</v>
       </c>
       <c r="D19" t="n">
-        <v>14.27</v>
+        <v>14.58</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F19" t="n">
-        <v>1712</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="20">
@@ -1117,19 +1117,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C20" t="n">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="D20" t="n">
-        <v>38</v>
+        <v>37.98</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F20" t="n">
-        <v>4560</v>
+        <v>4558</v>
       </c>
     </row>
     <row r="21">
@@ -1140,16 +1140,16 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="22">
@@ -1157,19 +1157,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>33.3</v>
+        <v>33</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E22" t="n">
-        <v>66.67</v>
+        <v>66</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="23">
@@ -1177,19 +1177,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="24">
@@ -1197,19 +1197,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="25">
@@ -1217,19 +1217,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="26">
@@ -1237,19 +1237,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="27">
@@ -1257,19 +1257,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="28">
@@ -1277,7 +1277,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -1286,7 +1286,7 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -1306,7 +1306,7 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -1317,7 +1317,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -1326,7 +1326,7 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1530,10 +1530,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2266.7</v>
+        <v>2267</v>
       </c>
       <c r="C2" t="n">
-        <v>3333.3</v>
+        <v>3333</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -1542,16 +1542,16 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>3333.3</v>
+        <v>3329</v>
       </c>
       <c r="G2" t="n">
-        <v>3333.3</v>
+        <v>3333</v>
       </c>
       <c r="H2" t="n">
-        <v>3333.3</v>
+        <v>3333</v>
       </c>
       <c r="I2" t="n">
-        <v>3333.3</v>
+        <v>3333</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -1560,16 +1560,16 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>3333.3</v>
+        <v>3333</v>
       </c>
       <c r="M2" t="n">
-        <v>3333.3</v>
+        <v>3333</v>
       </c>
       <c r="N2" t="n">
-        <v>3333.3</v>
+        <v>3333</v>
       </c>
       <c r="O2" t="n">
-        <v>3333.3</v>
+        <v>3333</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -1578,13 +1578,13 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>3333.3</v>
+        <v>3334</v>
       </c>
       <c r="S2" t="n">
-        <v>3618.7</v>
+        <v>3625</v>
       </c>
       <c r="T2" t="n">
-        <v>4093.3</v>
+        <v>4093</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>5000</v>
+        <v>4996</v>
       </c>
       <c r="K3" t="n">
         <v>5000</v>
@@ -1669,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>5000</v>
+        <v>4996</v>
       </c>
       <c r="Q3" t="n">
         <v>5000</v>
@@ -1684,7 +1684,7 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>3284</v>
+        <v>3292</v>
       </c>
       <c r="V3" t="n">
         <v>5000</v>
@@ -1757,7 +1757,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>5000</v>
+        <v>4998</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -1775,7 +1775,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>5000</v>
+        <v>4998</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1790,7 +1790,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>4142</v>
+        <v>4146</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>17500</v>
+        <v>17493</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1860,7 +1860,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>17500</v>
+        <v>17493</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -1875,7 +1875,7 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>14497</v>
+        <v>14511</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -1951,7 +1951,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3333.3</v>
+        <v>3332</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1969,7 +1969,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3333.3</v>
+        <v>3332</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1984,7 +1984,7 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2761.3</v>
+        <v>2764</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2500</v>
+        <v>2499</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -2069,7 +2069,7 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2500</v>
+        <v>2499</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2071</v>
+        <v>2073</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -2154,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>833.3</v>
+        <v>833</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -2172,7 +2172,7 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>833.3</v>
+        <v>833</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -2187,7 +2187,7 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>690.3</v>
+        <v>691</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -2489,7 +2489,7 @@
         <v>6400</v>
       </c>
       <c r="F2" t="n">
-        <v>8666.700000000001</v>
+        <v>8667</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -2501,13 +2501,13 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>3333.3</v>
+        <v>3329</v>
       </c>
       <c r="K2" t="n">
-        <v>6666.7</v>
+        <v>6662</v>
       </c>
       <c r="L2" t="n">
-        <v>10000</v>
+        <v>9995</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -2519,28 +2519,28 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>3333.3</v>
+        <v>3333</v>
       </c>
       <c r="Q2" t="n">
-        <v>6666.7</v>
+        <v>6666</v>
       </c>
       <c r="R2" t="n">
-        <v>10000</v>
+        <v>9999</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V2" t="n">
-        <v>3333.3</v>
+        <v>3338</v>
       </c>
       <c r="W2" t="n">
-        <v>6952</v>
+        <v>6963</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>5000</v>
+        <v>4996</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -2622,7 +2622,7 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>5000</v>
+        <v>4996</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -2637,7 +2637,7 @@
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>3284</v>
+        <v>3292</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -3104,37 +3104,37 @@
         <v>648</v>
       </c>
       <c r="Q8" t="n">
-        <v>1313.3</v>
+        <v>1313</v>
       </c>
       <c r="R8" t="n">
-        <v>1132.3</v>
+        <v>1132</v>
       </c>
       <c r="S8" t="n">
-        <v>944.3</v>
+        <v>944</v>
       </c>
       <c r="T8" t="n">
-        <v>732.3</v>
+        <v>732</v>
       </c>
       <c r="U8" t="n">
-        <v>479.3</v>
+        <v>479</v>
       </c>
       <c r="V8" t="n">
-        <v>260.3</v>
+        <v>260</v>
       </c>
       <c r="W8" t="n">
-        <v>897.7</v>
+        <v>897</v>
       </c>
       <c r="X8" t="n">
-        <v>671.7</v>
+        <v>671</v>
       </c>
       <c r="Y8" t="n">
-        <v>432.7</v>
+        <v>432</v>
       </c>
       <c r="Z8" t="n">
-        <v>212.7</v>
+        <v>212</v>
       </c>
       <c r="AA8" t="n">
-        <v>13.7</v>
+        <v>13</v>
       </c>
       <c r="AB8" t="n">
         <v>521</v>

--- a/output_3a.xlsx
+++ b/output_3a.xlsx
@@ -937,7 +937,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
         <v>-0</v>
@@ -946,7 +946,7 @@
         <v>-0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>-0</v>
@@ -977,7 +977,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
         <v>-0</v>
@@ -986,7 +986,7 @@
         <v>-0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
         <v>-0</v>
@@ -1137,7 +1137,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C21" t="n">
         <v>-0</v>
@@ -1146,7 +1146,7 @@
         <v>-0</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F21" t="n">
         <v>-0</v>
